--- a/results/0_excel_files/passive_attack_file_TEST_0.xlsx
+++ b/results/0_excel_files/passive_attack_file_TEST_0.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Bakalaura Darbs\!Code\Bakalaura_darbs\results\0_excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08C074E4-B17C-4255-8FDB-B4F754799CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0103069-307B-4093-AF0F-3871E3871E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{22EBAA71-89A5-4664-89F1-0CB54D81033C}"/>
   </bookViews>
@@ -41,18 +41,6 @@
     <t>Stego-method</t>
   </si>
   <si>
-    <t>TEST_0_stego_method_1</t>
-  </si>
-  <si>
-    <t>TEST_0_stego_method_4</t>
-  </si>
-  <si>
-    <t>TEST_0_stego_method_5</t>
-  </si>
-  <si>
-    <t>TEST_0_stego_method_6</t>
-  </si>
-  <si>
     <t>01_insert_attack</t>
   </si>
   <si>
@@ -126,13 +114,25 @@
   </si>
   <si>
     <t>Corruption percentage</t>
+  </si>
+  <si>
+    <t>hide_in_text</t>
+  </si>
+  <si>
+    <t>modify_RGB_color_ch</t>
+  </si>
+  <si>
+    <t>unispace</t>
+  </si>
+  <si>
+    <t>unicode_homoglyphs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,11 +143,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="186"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="186"/>
     </font>
   </fonts>
   <fills count="2">
@@ -336,54 +343,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -721,634 +733,626 @@
   <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="21.7109375" customWidth="1"/>
-    <col min="4" max="4" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="21.7109375" customWidth="1"/>
-    <col min="8" max="8" width="36.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="21.7109375" customWidth="1"/>
-    <col min="16" max="16" width="39.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="50" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="30.7109375" customWidth="1"/>
+    <col min="8" max="8" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="30.7109375" customWidth="1"/>
+    <col min="12" max="12" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="30.7109375" customWidth="1"/>
+    <col min="16" max="16" width="50" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="22.140625" customWidth="1"/>
     <col min="19" max="19" width="39.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+    </row>
+    <row r="2" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="5" t="s">
+      <c r="B3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="5" t="s">
+      <c r="D3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
+      <c r="E3" s="11">
+        <v>1.07</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="11">
+        <v>100</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="11">
+        <v>3.47</v>
+      </c>
+      <c r="N3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="P3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q3" s="13">
+        <v>100</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="15" t="s">
-        <v>29</v>
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="15">
+        <v>1.07</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="15">
+        <v>100</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="15">
+        <v>62.65</v>
+      </c>
+      <c r="N4" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q4" s="17">
+        <v>19.14</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="8">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="15">
         <v>1.07</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="F5" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="15">
+        <v>100</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="8">
-        <v>100</v>
-      </c>
-      <c r="J3" s="9" t="s">
+      <c r="L5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" s="8">
-        <v>3.47</v>
-      </c>
-      <c r="N3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q3" s="18">
-        <v>100</v>
+      <c r="M5" s="15">
+        <v>62.65</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O5" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="17">
+        <v>19.14</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="6">
-        <v>1.07</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="6">
-        <v>100</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="B6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="15">
+        <v>100</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I6" s="15">
+        <v>100</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="15">
+        <v>100</v>
+      </c>
+      <c r="N6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="B7" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="6">
-        <v>62.65</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q4" s="16">
-        <v>19.14</v>
+      <c r="E7" s="15">
+        <v>0</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="15">
+        <v>99.14</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="15">
+        <v>0</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="15">
+        <v>100</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="6">
-        <v>1.07</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="6">
-        <v>100</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" s="2" t="s">
+      <c r="H8" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="15">
+        <v>99.14</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="15">
+        <v>100</v>
+      </c>
+      <c r="N8" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O8" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="P8" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="15">
+        <v>100</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="15">
+        <v>100</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="15">
+        <v>100</v>
+      </c>
+      <c r="N9" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="15">
+        <v>100</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="15">
+        <v>100</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="15">
+        <v>100</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="P10" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="M5" s="6">
-        <v>62.65</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q5" s="16">
-        <v>19.14</v>
+      <c r="E11" s="15">
+        <v>0</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="15">
+        <v>0</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="M11" s="15">
+        <v>100</v>
+      </c>
+      <c r="N11" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O11" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q11" s="17">
+        <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="6">
-        <v>100</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="6">
-        <v>100</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="6">
-        <v>100</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q6" s="16">
+      <c r="I12" s="15">
+        <v>99.14</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="L12" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" s="15">
+        <v>100</v>
+      </c>
+      <c r="N12" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O12" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="17">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="6">
-        <v>99.14</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q7" s="16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="6">
-        <v>100</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="6">
-        <v>99.14</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M8" s="6">
-        <v>100</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="6">
-        <v>100</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="6">
-        <v>100</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M9" s="6">
-        <v>100</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q9" s="16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="6">
-        <v>100</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="6">
-        <v>100</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M10" s="6">
-        <v>100</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q10" s="16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="6">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M11" s="6">
-        <v>100</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q11" s="16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I12" s="6">
-        <v>99.14</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M12" s="6">
-        <v>100</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q12" s="16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="4:18" x14ac:dyDescent="0.25">
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-    </row>
-    <row r="20" spans="4:18" x14ac:dyDescent="0.25">
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-    </row>
-    <row r="25" spans="4:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="26" spans="4:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="R26" s="17"/>
+    <row r="25" spans="18:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="18:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R26" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
